--- a/descriptive tables/chronic_gender.xlsx
+++ b/descriptive tables/chronic_gender.xlsx
@@ -304,7 +304,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -329,22 +329,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>97</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>6.23</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -355,22 +343,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>525</v>
+        <v>796</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>518</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>33.25</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -381,22 +357,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>286</v>
+        <v>442</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>219</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>14.06</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -407,22 +371,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>86</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>5.52</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -433,22 +385,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>63</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>4.04</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -459,22 +399,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>0.71</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -485,22 +413,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <v>0.06</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -511,22 +427,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>1.35</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -537,22 +441,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -563,22 +455,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -592,19 +472,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -615,22 +483,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="E13" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>194</v>
-      </c>
-      <c r="H13" s="0" t="n">
-        <v>12.45</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -641,22 +497,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="E14" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>89</v>
-      </c>
-      <c r="H14" s="0" t="n">
-        <v>5.71</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -667,22 +511,10 @@
         <v>15</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E15" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="G15" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="0" t="n">
-        <v>0.45</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -693,22 +525,10 @@
         <v>16</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <v>56</v>
-      </c>
-      <c r="H16" s="0" t="n">
-        <v>3.59</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,22 +539,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E17" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" s="0" t="n">
-        <v>54</v>
-      </c>
-      <c r="H17" s="0" t="n">
-        <v>3.47</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -745,52 +553,279 @@
         <v>96</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="E18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="0" t="n">
+        <v>10.57</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>798</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>374</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>13.55</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>437</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>15.83</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="G18" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="0" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="0" t="n">
+      <c r="C35" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="G19" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="H19" s="0" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="0" t="n">
+      <c r="C36" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="0" t="n">
         <v>96</v>
       </c>
-      <c r="G20" s="0" t="n">
-        <v>107</v>
-      </c>
-      <c r="H20" s="0" t="n">
-        <v>6.87</v>
-      </c>
-    </row>
+      <c r="C37" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
